--- a/Data/Hubs_Data_Actual.xlsx
+++ b/Data/Hubs_Data_Actual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mottmac-my.sharepoint.com/personal/jonathan_field_mottmac_com/Documents/Documents/CCm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC3E093C-5DF6-4AC3-A192-48C52FDDF606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{FC3E093C-5DF6-4AC3-A192-48C52FDDF606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17C88B13-FB13-4C99-80E3-F10B60E3FF36}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -461,7 +461,7 @@
         <v>0.05</v>
       </c>
       <c r="G2">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -484,7 +484,7 @@
         <v>0.05</v>
       </c>
       <c r="G3">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -507,7 +507,7 @@
         <v>0.05</v>
       </c>
       <c r="G4">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -530,7 +530,7 @@
         <v>0.05</v>
       </c>
       <c r="G5">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -553,7 +553,7 @@
         <v>0.05</v>
       </c>
       <c r="G6">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -576,7 +576,7 @@
         <v>0.05</v>
       </c>
       <c r="G7">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -599,7 +599,7 @@
         <v>0.05</v>
       </c>
       <c r="G8">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -622,7 +622,7 @@
         <v>0.05</v>
       </c>
       <c r="G9">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -645,7 +645,7 @@
         <v>0.05</v>
       </c>
       <c r="G10">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -668,7 +668,7 @@
         <v>0.05</v>
       </c>
       <c r="G11">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -691,7 +691,7 @@
         <v>0.05</v>
       </c>
       <c r="G12">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -714,7 +714,7 @@
         <v>0.05</v>
       </c>
       <c r="G13">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -737,7 +737,7 @@
         <v>0.05</v>
       </c>
       <c r="G14">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -760,7 +760,7 @@
         <v>0.05</v>
       </c>
       <c r="G15">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -783,7 +783,7 @@
         <v>0.05</v>
       </c>
       <c r="G16">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -806,7 +806,7 @@
         <v>0.05</v>
       </c>
       <c r="G17">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -829,7 +829,7 @@
         <v>0.05</v>
       </c>
       <c r="G18">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
         <v>0.05</v>
       </c>
       <c r="G19">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -875,7 +875,7 @@
         <v>0.05</v>
       </c>
       <c r="G20">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -898,7 +898,7 @@
         <v>0.05</v>
       </c>
       <c r="G21">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -921,7 +921,7 @@
         <v>0.05</v>
       </c>
       <c r="G22">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -944,7 +944,7 @@
         <v>0.05</v>
       </c>
       <c r="G23">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>0.05</v>
       </c>
       <c r="G24">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -990,7 +990,7 @@
         <v>0.05</v>
       </c>
       <c r="G25">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1013,7 +1013,7 @@
         <v>0.05</v>
       </c>
       <c r="G26">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1036,7 +1036,7 @@
         <v>0.05</v>
       </c>
       <c r="G27">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1059,7 +1059,7 @@
         <v>0.05</v>
       </c>
       <c r="G28">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1082,7 +1082,7 @@
         <v>0.05</v>
       </c>
       <c r="G29">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
         <v>0.05</v>
       </c>
       <c r="G30">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1128,7 +1128,7 @@
         <v>0.05</v>
       </c>
       <c r="G31">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1151,7 +1151,7 @@
         <v>0.05</v>
       </c>
       <c r="G32">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -1174,7 +1174,7 @@
         <v>0.05</v>
       </c>
       <c r="G33">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1197,7 +1197,7 @@
         <v>0.05</v>
       </c>
       <c r="G34">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1220,7 +1220,7 @@
         <v>0.05</v>
       </c>
       <c r="G35">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1243,7 +1243,7 @@
         <v>0.05</v>
       </c>
       <c r="G36">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1266,7 +1266,7 @@
         <v>0.05</v>
       </c>
       <c r="G37">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1289,7 +1289,7 @@
         <v>0.05</v>
       </c>
       <c r="G38">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1312,7 +1312,7 @@
         <v>0.05</v>
       </c>
       <c r="G39">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1335,7 +1335,7 @@
         <v>0.05</v>
       </c>
       <c r="G40">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1358,7 +1358,7 @@
         <v>0.05</v>
       </c>
       <c r="G41">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1381,7 +1381,7 @@
         <v>0.05</v>
       </c>
       <c r="G42">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1404,7 +1404,7 @@
         <v>0.05</v>
       </c>
       <c r="G43">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1427,7 +1427,7 @@
         <v>0.05</v>
       </c>
       <c r="G44">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
         <v>0.05</v>
       </c>
       <c r="G45">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1473,7 +1473,7 @@
         <v>0.05</v>
       </c>
       <c r="G46">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1496,7 +1496,7 @@
         <v>0.05</v>
       </c>
       <c r="G47">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1519,7 +1519,7 @@
         <v>0.05</v>
       </c>
       <c r="G48">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1542,7 +1542,7 @@
         <v>0.05</v>
       </c>
       <c r="G49">
-        <v>10000</v>
+        <v>50000</v>
       </c>
     </row>
   </sheetData>
